--- a/Documentos/3.1.3 Planilla Casos de Prueba(1).xlsx
+++ b/Documentos/3.1.3 Planilla Casos de Prueba(1).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenop\OneDrive\Documentos\GitHub\Pripelu\Documentos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25C858B-E887-4506-8F29-042359C31A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834277D8-BFCB-4D0A-9C7E-22F94F3EDFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pruebas Estandar " sheetId="3" r:id="rId1"/>
@@ -2010,10 +2010,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2051,53 +2099,29 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2105,44 +2129,20 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2293,10 +2293,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2947,6 +2953,60 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>594360</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="AutoShape 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7143383-F9B2-711C-9602-14AD69748433}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9928860" cy="13525500"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3281,26 +3341,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" style="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="113.5703125" style="25" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" style="25" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" style="25" customWidth="1"/>
-    <col min="6" max="6" width="38.42578125" style="25" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" style="25" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" style="25" customWidth="1"/>
+    <col min="3" max="3" width="113.5546875" style="25" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" style="25" customWidth="1"/>
+    <col min="6" max="6" width="38.44140625" style="25" customWidth="1"/>
+    <col min="7" max="7" width="5.109375" style="25" customWidth="1"/>
     <col min="8" max="8" width="4" style="25" customWidth="1"/>
-    <col min="9" max="9" width="4.5703125" style="25" customWidth="1"/>
-    <col min="10" max="10" width="34.7109375" style="25" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="25"/>
+    <col min="9" max="9" width="4.5546875" style="25" customWidth="1"/>
+    <col min="10" max="10" width="34.6640625" style="25" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1">
-      <c r="B1" s="115" t="s">
+      <c r="B1" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="115"/>
+      <c r="C1" s="121"/>
       <c r="D1" s="45"/>
       <c r="E1" s="45"/>
       <c r="F1" s="45"/>
@@ -3326,11 +3386,11 @@
       <c r="J2" s="42"/>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1">
-      <c r="B3" s="119" t="s">
+      <c r="B3" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="120"/>
-      <c r="D3" s="121"/>
+      <c r="C3" s="111"/>
+      <c r="D3" s="112"/>
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
       <c r="G3" s="38"/>
@@ -3338,12 +3398,12 @@
       <c r="I3" s="38"/>
       <c r="J3" s="38"/>
     </row>
-    <row r="4" spans="1:15" ht="17.25" thickBot="1">
-      <c r="B4" s="116" t="s">
+    <row r="4" spans="1:15" ht="16.8" thickBot="1">
+      <c r="B4" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="118"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="109"/>
       <c r="E4" s="39"/>
       <c r="F4" s="38"/>
       <c r="G4" s="38"/>
@@ -3366,10 +3426,10 @@
       <c r="A6" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="111" t="s">
+      <c r="B6" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="112"/>
+      <c r="C6" s="118"/>
       <c r="D6" s="64" t="s">
         <v>5</v>
       </c>
@@ -3397,10 +3457,10 @@
       <c r="A8" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="108"/>
+      <c r="C8" s="116"/>
       <c r="D8" s="33" t="s">
         <v>81</v>
       </c>
@@ -3410,10 +3470,10 @@
       <c r="A9" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="108"/>
+      <c r="C9" s="116"/>
       <c r="D9" s="33" t="s">
         <v>81</v>
       </c>
@@ -3421,92 +3481,92 @@
     </row>
     <row r="10" spans="1:15" ht="15" customHeight="1">
       <c r="A10" s="29"/>
-      <c r="B10" s="107"/>
-      <c r="C10" s="108"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="116"/>
       <c r="D10" s="33"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:15" ht="15" customHeight="1">
       <c r="A11" s="29"/>
-      <c r="B11" s="107"/>
-      <c r="C11" s="108"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="116"/>
       <c r="D11" s="33"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:15" ht="15" customHeight="1">
       <c r="A12" s="29"/>
-      <c r="B12" s="107"/>
-      <c r="C12" s="108"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="116"/>
       <c r="D12" s="33"/>
       <c r="E12" s="34"/>
     </row>
     <row r="13" spans="1:15" ht="15" customHeight="1">
       <c r="A13" s="29"/>
-      <c r="B13" s="107"/>
-      <c r="C13" s="108"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="116"/>
       <c r="D13" s="33"/>
       <c r="E13" s="34"/>
     </row>
     <row r="14" spans="1:15" ht="15" customHeight="1">
       <c r="A14" s="29"/>
-      <c r="B14" s="107"/>
-      <c r="C14" s="108"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="116"/>
       <c r="D14" s="33"/>
       <c r="E14" s="34"/>
     </row>
     <row r="15" spans="1:15" ht="15" customHeight="1">
       <c r="A15" s="29"/>
-      <c r="B15" s="107"/>
-      <c r="C15" s="108"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="116"/>
       <c r="D15" s="33"/>
       <c r="E15" s="34"/>
     </row>
     <row r="16" spans="1:15" ht="15" customHeight="1">
       <c r="A16" s="29"/>
-      <c r="B16" s="107"/>
-      <c r="C16" s="108"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="116"/>
       <c r="D16" s="33"/>
       <c r="E16" s="34"/>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1">
       <c r="A17" s="29"/>
-      <c r="B17" s="107"/>
-      <c r="C17" s="108"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="116"/>
       <c r="D17" s="33"/>
       <c r="E17" s="34"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1">
       <c r="A18" s="29"/>
-      <c r="B18" s="107"/>
-      <c r="C18" s="108"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="116"/>
       <c r="D18" s="33"/>
       <c r="E18" s="34"/>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1">
       <c r="A19" s="29"/>
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="116"/>
       <c r="D19" s="33"/>
       <c r="E19" s="34"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1">
       <c r="A20" s="29"/>
-      <c r="B20" s="107"/>
-      <c r="C20" s="108"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="116"/>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1">
       <c r="A21" s="29"/>
-      <c r="B21" s="107"/>
-      <c r="C21" s="108"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="116"/>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" thickBot="1">
       <c r="A22" s="27"/>
-      <c r="B22" s="109"/>
-      <c r="C22" s="110"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="120"/>
       <c r="D22" s="32"/>
       <c r="E22" s="34"/>
     </row>
@@ -3518,10 +3578,10 @@
       <c r="A24" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B24" s="111" t="s">
+      <c r="B24" s="117" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="112"/>
+      <c r="C24" s="118"/>
       <c r="D24" s="65"/>
       <c r="E24" s="34"/>
     </row>
@@ -3542,10 +3602,10 @@
       <c r="A26" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="108"/>
+      <c r="C26" s="116"/>
       <c r="D26" s="33" t="s">
         <v>81</v>
       </c>
@@ -3555,10 +3615,10 @@
       <c r="A27" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="107" t="s">
+      <c r="B27" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="108"/>
+      <c r="C27" s="116"/>
       <c r="D27" s="33" t="s">
         <v>81</v>
       </c>
@@ -3566,98 +3626,98 @@
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1">
       <c r="A28" s="29"/>
-      <c r="B28" s="107"/>
-      <c r="C28" s="108"/>
+      <c r="B28" s="115"/>
+      <c r="C28" s="116"/>
       <c r="D28" s="33"/>
       <c r="E28" s="34"/>
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1">
       <c r="A29" s="29"/>
-      <c r="B29" s="107"/>
-      <c r="C29" s="108"/>
+      <c r="B29" s="115"/>
+      <c r="C29" s="116"/>
       <c r="D29" s="33"/>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1">
       <c r="A30" s="29"/>
-      <c r="B30" s="107"/>
-      <c r="C30" s="108"/>
+      <c r="B30" s="115"/>
+      <c r="C30" s="116"/>
       <c r="D30" s="33"/>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1">
       <c r="A31" s="29"/>
-      <c r="B31" s="107"/>
-      <c r="C31" s="108"/>
+      <c r="B31" s="115"/>
+      <c r="C31" s="116"/>
       <c r="D31" s="33"/>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1">
       <c r="A32" s="29"/>
-      <c r="B32" s="107"/>
-      <c r="C32" s="108"/>
+      <c r="B32" s="115"/>
+      <c r="C32" s="116"/>
       <c r="D32" s="33"/>
     </row>
     <row r="33" spans="1:4" ht="15" customHeight="1">
       <c r="A33" s="29"/>
-      <c r="B33" s="107"/>
-      <c r="C33" s="108"/>
+      <c r="B33" s="115"/>
+      <c r="C33" s="116"/>
       <c r="D33" s="33"/>
     </row>
     <row r="34" spans="1:4" ht="15" customHeight="1">
       <c r="A34" s="29"/>
-      <c r="B34" s="107"/>
-      <c r="C34" s="108"/>
+      <c r="B34" s="115"/>
+      <c r="C34" s="116"/>
       <c r="D34" s="33"/>
     </row>
     <row r="35" spans="1:4" ht="15" customHeight="1">
       <c r="A35" s="29"/>
-      <c r="B35" s="107"/>
-      <c r="C35" s="108"/>
+      <c r="B35" s="115"/>
+      <c r="C35" s="116"/>
       <c r="D35" s="33"/>
     </row>
     <row r="36" spans="1:4" ht="15" customHeight="1">
       <c r="A36" s="29"/>
-      <c r="B36" s="107"/>
-      <c r="C36" s="108"/>
+      <c r="B36" s="115"/>
+      <c r="C36" s="116"/>
       <c r="D36" s="33"/>
     </row>
     <row r="37" spans="1:4" ht="15" customHeight="1">
       <c r="A37" s="29"/>
-      <c r="B37" s="107"/>
-      <c r="C37" s="108"/>
+      <c r="B37" s="115"/>
+      <c r="C37" s="116"/>
       <c r="D37" s="33"/>
     </row>
     <row r="38" spans="1:4" ht="15" customHeight="1">
       <c r="A38" s="29"/>
-      <c r="B38" s="107"/>
-      <c r="C38" s="108"/>
+      <c r="B38" s="115"/>
+      <c r="C38" s="116"/>
       <c r="D38" s="33"/>
     </row>
     <row r="39" spans="1:4" ht="15" customHeight="1">
       <c r="A39" s="29"/>
-      <c r="B39" s="107"/>
-      <c r="C39" s="108"/>
+      <c r="B39" s="115"/>
+      <c r="C39" s="116"/>
       <c r="D39" s="33"/>
     </row>
     <row r="40" spans="1:4" ht="15" customHeight="1">
       <c r="A40" s="29"/>
-      <c r="B40" s="107"/>
-      <c r="C40" s="108"/>
+      <c r="B40" s="115"/>
+      <c r="C40" s="116"/>
       <c r="D40" s="33"/>
     </row>
     <row r="41" spans="1:4" ht="15" customHeight="1" thickBot="1">
       <c r="A41" s="27"/>
-      <c r="B41" s="109"/>
-      <c r="C41" s="110"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="120"/>
       <c r="D41" s="32"/>
     </row>
     <row r="42" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1"/>
-    <row r="43" spans="1:4" ht="18.75" thickBot="1">
+    <row r="43" spans="1:4" ht="18" thickBot="1">
       <c r="A43" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B43" s="111" t="s">
+      <c r="B43" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="112"/>
+      <c r="C43" s="118"/>
       <c r="D43" s="66"/>
     </row>
     <row r="44" spans="1:4" ht="15" customHeight="1">
@@ -3676,10 +3736,10 @@
       <c r="A45" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B45" s="107" t="s">
+      <c r="B45" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="C45" s="108"/>
+      <c r="C45" s="116"/>
       <c r="D45" s="33" t="s">
         <v>81</v>
       </c>
@@ -3688,95 +3748,95 @@
       <c r="A46" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="107" t="s">
+      <c r="B46" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="C46" s="108"/>
+      <c r="C46" s="116"/>
       <c r="D46" s="33" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15" customHeight="1">
       <c r="A47" s="29"/>
-      <c r="B47" s="107"/>
-      <c r="C47" s="108"/>
+      <c r="B47" s="115"/>
+      <c r="C47" s="116"/>
       <c r="D47" s="29"/>
     </row>
     <row r="48" spans="1:4" ht="15" customHeight="1">
       <c r="A48" s="29"/>
-      <c r="B48" s="107"/>
-      <c r="C48" s="108"/>
+      <c r="B48" s="115"/>
+      <c r="C48" s="116"/>
       <c r="D48" s="29"/>
     </row>
     <row r="49" spans="1:4" ht="15" customHeight="1">
       <c r="A49" s="29"/>
-      <c r="B49" s="107"/>
-      <c r="C49" s="108"/>
+      <c r="B49" s="115"/>
+      <c r="C49" s="116"/>
       <c r="D49" s="29"/>
     </row>
     <row r="50" spans="1:4" ht="15" customHeight="1">
       <c r="A50" s="29"/>
-      <c r="B50" s="107"/>
-      <c r="C50" s="108"/>
+      <c r="B50" s="115"/>
+      <c r="C50" s="116"/>
       <c r="D50" s="29"/>
     </row>
     <row r="51" spans="1:4" ht="15" customHeight="1">
       <c r="A51" s="29"/>
-      <c r="B51" s="107"/>
-      <c r="C51" s="108"/>
+      <c r="B51" s="115"/>
+      <c r="C51" s="116"/>
       <c r="D51" s="29"/>
     </row>
     <row r="52" spans="1:4" ht="15" customHeight="1">
       <c r="A52" s="29"/>
-      <c r="B52" s="107"/>
-      <c r="C52" s="108"/>
+      <c r="B52" s="115"/>
+      <c r="C52" s="116"/>
       <c r="D52" s="29"/>
     </row>
     <row r="53" spans="1:4" ht="15" customHeight="1">
       <c r="A53" s="29"/>
-      <c r="B53" s="107"/>
-      <c r="C53" s="108"/>
+      <c r="B53" s="115"/>
+      <c r="C53" s="116"/>
       <c r="D53" s="29"/>
     </row>
     <row r="54" spans="1:4" ht="15" customHeight="1">
       <c r="A54" s="29"/>
-      <c r="B54" s="107"/>
-      <c r="C54" s="108"/>
+      <c r="B54" s="115"/>
+      <c r="C54" s="116"/>
       <c r="D54" s="29"/>
     </row>
     <row r="55" spans="1:4" ht="15" customHeight="1">
       <c r="A55" s="29"/>
-      <c r="B55" s="107"/>
-      <c r="C55" s="108"/>
+      <c r="B55" s="115"/>
+      <c r="C55" s="116"/>
       <c r="D55" s="29"/>
     </row>
     <row r="56" spans="1:4" ht="15" customHeight="1">
       <c r="A56" s="29"/>
-      <c r="B56" s="107"/>
-      <c r="C56" s="108"/>
+      <c r="B56" s="115"/>
+      <c r="C56" s="116"/>
       <c r="D56" s="29"/>
     </row>
     <row r="57" spans="1:4" ht="15" customHeight="1">
       <c r="A57" s="29"/>
-      <c r="B57" s="107"/>
-      <c r="C57" s="108"/>
+      <c r="B57" s="115"/>
+      <c r="C57" s="116"/>
       <c r="D57" s="29"/>
     </row>
     <row r="58" spans="1:4" ht="15" customHeight="1" thickBot="1">
       <c r="A58" s="27"/>
-      <c r="B58" s="109"/>
-      <c r="C58" s="110"/>
+      <c r="B58" s="119"/>
+      <c r="C58" s="120"/>
       <c r="D58" s="27"/>
     </row>
     <row r="59" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1"/>
-    <row r="60" spans="1:4" ht="18.75" thickBot="1">
+    <row r="60" spans="1:4" ht="18" thickBot="1">
       <c r="A60" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B60" s="111" t="s">
+      <c r="B60" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="C60" s="112"/>
+      <c r="C60" s="118"/>
       <c r="D60" s="66"/>
     </row>
     <row r="61" spans="1:4" ht="15" customHeight="1">
@@ -3795,10 +3855,10 @@
       <c r="A62" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B62" s="107" t="s">
+      <c r="B62" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="C62" s="108"/>
+      <c r="C62" s="116"/>
       <c r="D62" s="33" t="s">
         <v>81</v>
       </c>
@@ -3835,22 +3895,22 @@
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1" thickBot="1">
       <c r="A67" s="27"/>
-      <c r="B67" s="109"/>
-      <c r="C67" s="110"/>
+      <c r="B67" s="119"/>
+      <c r="C67" s="120"/>
       <c r="D67" s="27"/>
     </row>
     <row r="68" spans="1:4" ht="15" customHeight="1">
       <c r="B68" s="60"/>
     </row>
     <row r="69" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1"/>
-    <row r="70" spans="1:4" ht="18.75" thickBot="1">
+    <row r="70" spans="1:4" ht="18" thickBot="1">
       <c r="A70" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B70" s="111" t="s">
+      <c r="B70" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="C70" s="112"/>
+      <c r="C70" s="118"/>
       <c r="D70" s="66"/>
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1" thickBot="1">
@@ -3869,10 +3929,10 @@
       <c r="A72" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B72" s="107" t="s">
+      <c r="B72" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="C72" s="108"/>
+      <c r="C72" s="116"/>
       <c r="D72" s="68" t="s">
         <v>98</v>
       </c>
@@ -3891,34 +3951,34 @@
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1">
       <c r="A75" s="29"/>
-      <c r="B75" s="107"/>
-      <c r="C75" s="108"/>
+      <c r="B75" s="115"/>
+      <c r="C75" s="116"/>
       <c r="D75" s="29"/>
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1">
       <c r="A76" s="29"/>
-      <c r="B76" s="107"/>
-      <c r="C76" s="108"/>
+      <c r="B76" s="115"/>
+      <c r="C76" s="116"/>
       <c r="D76" s="29"/>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1" thickBot="1">
       <c r="A77" s="27"/>
-      <c r="B77" s="109"/>
-      <c r="C77" s="110"/>
+      <c r="B77" s="119"/>
+      <c r="C77" s="120"/>
       <c r="D77" s="27"/>
     </row>
     <row r="78" spans="1:4" ht="20.100000000000001" customHeight="1" thickBot="1"/>
-    <row r="79" spans="1:4" ht="18.75" thickBot="1">
+    <row r="79" spans="1:4" ht="18" thickBot="1">
       <c r="A79" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="B79" s="111" t="s">
+      <c r="B79" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="C79" s="112"/>
+      <c r="C79" s="118"/>
       <c r="D79" s="66"/>
     </row>
-    <row r="80" spans="1:4" ht="14.25">
+    <row r="80" spans="1:4" ht="13.8">
       <c r="A80" s="31" t="s">
         <v>39</v>
       </c>
@@ -3926,15 +3986,15 @@
       <c r="C80" s="114"/>
       <c r="D80" s="30"/>
     </row>
-    <row r="81" spans="1:4" ht="14.25">
+    <row r="81" spans="1:4" ht="13.8">
       <c r="A81" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B81" s="107"/>
-      <c r="C81" s="108"/>
+      <c r="B81" s="115"/>
+      <c r="C81" s="116"/>
       <c r="D81" s="30"/>
     </row>
-    <row r="82" spans="1:4" ht="14.25">
+    <row r="82" spans="1:4" ht="13.8">
       <c r="A82" s="29" t="s">
         <v>41</v>
       </c>
@@ -3942,93 +4002,51 @@
       <c r="C82" s="59"/>
       <c r="D82" s="30"/>
     </row>
-    <row r="83" spans="1:4" ht="14.25">
+    <row r="83" spans="1:4" ht="13.8">
       <c r="A83" s="29"/>
       <c r="B83" s="58"/>
       <c r="C83" s="59"/>
       <c r="D83" s="30"/>
     </row>
-    <row r="84" spans="1:4" ht="14.25">
+    <row r="84" spans="1:4" ht="13.8">
       <c r="A84" s="29"/>
       <c r="B84" s="58"/>
       <c r="C84" s="59"/>
       <c r="D84" s="30"/>
     </row>
-    <row r="85" spans="1:4" ht="14.25">
-      <c r="B85" s="107"/>
-      <c r="C85" s="108"/>
+    <row r="85" spans="1:4" ht="13.8">
+      <c r="B85" s="115"/>
+      <c r="C85" s="116"/>
       <c r="D85" s="29"/>
     </row>
-    <row r="86" spans="1:4" ht="14.25">
+    <row r="86" spans="1:4" ht="13.8">
       <c r="A86" s="29"/>
-      <c r="B86" s="107"/>
-      <c r="C86" s="108"/>
+      <c r="B86" s="115"/>
+      <c r="C86" s="116"/>
       <c r="D86" s="28"/>
     </row>
-    <row r="87" spans="1:4" ht="15" thickBot="1">
+    <row r="87" spans="1:4" ht="14.4" thickBot="1">
       <c r="A87" s="27"/>
-      <c r="B87" s="109"/>
-      <c r="C87" s="110"/>
+      <c r="B87" s="119"/>
+      <c r="C87" s="120"/>
       <c r="D87" s="27"/>
     </row>
-    <row r="88" spans="1:4" ht="14.25">
+    <row r="88" spans="1:4" ht="13.8">
       <c r="B88" s="26"/>
       <c r="C88" s="26"/>
     </row>
-    <row r="89" spans="1:4" ht="14.25">
+    <row r="89" spans="1:4" ht="13.8">
       <c r="B89" s="26"/>
       <c r="C89" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="70">
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B85:C85"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B72:C72"/>
     <mergeCell ref="B75:C75"/>
@@ -4045,12 +4063,54 @@
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="B55:C55"/>
     <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.67" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup scale="57" orientation="portrait" r:id="rId1"/>
@@ -4061,24 +4121,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X163"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="17.28515625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17.33203125" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="8.140625" style="6" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" style="6" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" style="6" customWidth="1"/>
     <col min="4" max="4" width="19" style="6" customWidth="1"/>
     <col min="5" max="5" width="9" style="6" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="33.42578125" style="6" customWidth="1"/>
-    <col min="8" max="8" width="26.28515625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="49.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" style="6" customWidth="1"/>
+    <col min="7" max="7" width="33.44140625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="26.33203125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="49.6640625" style="6" customWidth="1"/>
     <col min="10" max="10" width="5" style="6" customWidth="1"/>
     <col min="11" max="11" width="4" style="6" customWidth="1"/>
-    <col min="12" max="12" width="4.5703125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="12.85546875" style="6" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="33.28515625" style="6" customWidth="1"/>
-    <col min="15" max="24" width="11.42578125" style="6" customWidth="1"/>
-    <col min="25" max="16384" width="17.28515625" style="6"/>
+    <col min="12" max="12" width="4.5546875" style="6" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" style="6" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="33.33203125" style="6" customWidth="1"/>
+    <col min="15" max="24" width="11.44140625" style="6" customWidth="1"/>
+    <col min="25" max="16384" width="17.33203125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
@@ -4107,17 +4167,17 @@
     </row>
     <row r="2" spans="1:24" ht="19.5" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="88"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
       <c r="M2" s="4"/>
@@ -4131,17 +4191,17 @@
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
     </row>
-    <row r="3" spans="1:24" ht="19.5">
+    <row r="3" spans="1:24" ht="20.399999999999999">
       <c r="A3" s="1"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="88"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="88"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="88"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="88"/>
       <c r="K3" s="4"/>
       <c r="L3" s="5"/>
       <c r="M3" s="4"/>
@@ -4158,8 +4218,8 @@
     <row r="4" spans="1:24">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="80"/>
-      <c r="D4" s="79"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="88"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -4180,19 +4240,19 @@
       <c r="V4" s="4"/>
     </row>
     <row r="5" spans="1:24">
-      <c r="A5" s="87" t="s">
+      <c r="A5" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="88" t="s">
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+      <c r="H5" s="102"/>
+      <c r="I5" s="102"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -4208,19 +4268,19 @@
       <c r="V5" s="10"/>
     </row>
     <row r="6" spans="1:24">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88" t="s">
+      <c r="B6" s="101"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -4236,19 +4296,19 @@
       <c r="V6" s="10"/>
     </row>
     <row r="7" spans="1:24">
-      <c r="A7" s="87" t="s">
+      <c r="A7" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="87"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88" t="s">
+      <c r="B7" s="101"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="102" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -4264,19 +4324,19 @@
       <c r="V7" s="10"/>
     </row>
     <row r="8" spans="1:24">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="87"/>
-      <c r="C8" s="87"/>
-      <c r="D8" s="88" t="s">
+      <c r="B8" s="101"/>
+      <c r="C8" s="101"/>
+      <c r="D8" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="88"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+      <c r="H8" s="102"/>
+      <c r="I8" s="102"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -4292,19 +4352,19 @@
       <c r="V8" s="10"/>
     </row>
     <row r="9" spans="1:24">
-      <c r="A9" s="90" t="s">
+      <c r="A9" s="104" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="91"/>
-      <c r="C9" s="92"/>
-      <c r="D9" s="99">
+      <c r="B9" s="105"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="90">
         <v>1</v>
       </c>
-      <c r="E9" s="100"/>
-      <c r="F9" s="100"/>
-      <c r="G9" s="100"/>
-      <c r="H9" s="100"/>
-      <c r="I9" s="101"/>
+      <c r="E9" s="91"/>
+      <c r="F9" s="91"/>
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="92"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -4320,19 +4380,19 @@
       <c r="V9" s="10"/>
     </row>
     <row r="10" spans="1:24">
-      <c r="A10" s="87" t="s">
+      <c r="A10" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="87"/>
-      <c r="C10" s="87"/>
-      <c r="D10" s="89">
+      <c r="B10" s="101"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="103">
         <v>46181</v>
       </c>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -4347,23 +4407,23 @@
       <c r="U10" s="10"/>
       <c r="V10" s="10"/>
     </row>
-    <row r="11" spans="1:24" ht="23.25" thickBot="1">
+    <row r="11" spans="1:24" ht="23.4" thickBot="1">
       <c r="A11" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B11" s="10"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="82"/>
-      <c r="G11" s="82"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="82"/>
-      <c r="J11" s="82"/>
-      <c r="K11" s="82"/>
-      <c r="L11" s="82"/>
-      <c r="M11" s="82"/>
-      <c r="N11" s="82"/>
+      <c r="C11" s="95"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="97"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
       <c r="O11" s="10"/>
       <c r="P11" s="10"/>
       <c r="Q11" s="10"/>
@@ -4375,7 +4435,7 @@
       <c r="W11" s="10"/>
       <c r="X11" s="10"/>
     </row>
-    <row r="12" spans="1:24" ht="32.25" thickBot="1">
+    <row r="12" spans="1:24" ht="23.4" thickBot="1">
       <c r="A12" s="11" t="s">
         <v>51</v>
       </c>
@@ -4403,13 +4463,13 @@
       <c r="I12" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="J12" s="84" t="s">
+      <c r="J12" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
-      <c r="N12" s="86"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="100"/>
       <c r="O12" s="14"/>
       <c r="P12" s="14"/>
       <c r="Q12" s="14"/>
@@ -4421,7 +4481,7 @@
       <c r="W12" s="14"/>
       <c r="X12" s="14"/>
     </row>
-    <row r="13" spans="1:24" ht="13.5" thickBot="1">
+    <row r="13" spans="1:24" ht="13.8" thickBot="1">
       <c r="A13" s="15"/>
       <c r="B13" s="15"/>
       <c r="C13" s="16"/>
@@ -4457,7 +4517,7 @@
       <c r="W13" s="14"/>
       <c r="X13" s="14"/>
     </row>
-    <row r="14" spans="1:24" ht="38.25">
+    <row r="14" spans="1:24" ht="39.6">
       <c r="A14" s="50">
         <v>1</v>
       </c>
@@ -4473,13 +4533,13 @@
       <c r="E14" s="21">
         <v>1</v>
       </c>
-      <c r="F14" s="94" t="s">
+      <c r="F14" s="78" t="s">
         <v>82</v>
       </c>
       <c r="G14" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="H14" s="102" t="s">
+      <c r="H14" s="93" t="s">
         <v>128</v>
       </c>
       <c r="I14" s="49" t="s">
@@ -4505,25 +4565,25 @@
       <c r="W14" s="22"/>
       <c r="X14" s="22"/>
     </row>
-    <row r="15" spans="1:24" ht="51">
-      <c r="A15" s="98"/>
-      <c r="B15" s="98"/>
-      <c r="C15" s="98"/>
-      <c r="D15" s="98"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="95"/>
+    <row r="15" spans="1:24" ht="52.8">
+      <c r="A15" s="83"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
+      <c r="D15" s="83"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="79"/>
       <c r="G15" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="102"/>
+      <c r="H15" s="93"/>
       <c r="I15" s="55" t="s">
         <v>130</v>
       </c>
-      <c r="J15" s="103"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="104"/>
-      <c r="M15" s="104"/>
-      <c r="N15" s="104"/>
+      <c r="J15" s="85"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="86"/>
+      <c r="N15" s="86"/>
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
       <c r="Q15" s="22"/>
@@ -4535,25 +4595,25 @@
       <c r="W15" s="22"/>
       <c r="X15" s="22"/>
     </row>
-    <row r="16" spans="1:24" ht="51.75" thickBot="1">
-      <c r="A16" s="98"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="96"/>
+    <row r="16" spans="1:24" ht="53.4" thickBot="1">
+      <c r="A16" s="83"/>
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="80"/>
       <c r="G16" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="H16" s="102"/>
+      <c r="H16" s="93"/>
       <c r="I16" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="J16" s="104"/>
-      <c r="K16" s="104"/>
-      <c r="L16" s="104"/>
-      <c r="M16" s="104"/>
-      <c r="N16" s="104"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
       <c r="Q16" s="22"/>
@@ -4565,7 +4625,7 @@
       <c r="W16" s="22"/>
       <c r="X16" s="22"/>
     </row>
-    <row r="17" spans="1:24" ht="70.900000000000006" customHeight="1">
+    <row r="17" spans="1:24" ht="70.95" customHeight="1">
       <c r="A17" s="50">
         <v>2</v>
       </c>
@@ -4581,13 +4641,13 @@
       <c r="E17" s="21">
         <v>2</v>
       </c>
-      <c r="F17" s="94" t="s">
+      <c r="F17" s="78" t="s">
         <v>83</v>
       </c>
       <c r="G17" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="H17" s="97" t="s">
+      <c r="H17" s="89" t="s">
         <v>135</v>
       </c>
       <c r="I17" s="49" t="s">
@@ -4613,25 +4673,25 @@
       <c r="W17" s="22"/>
       <c r="X17" s="22"/>
     </row>
-    <row r="18" spans="1:24" ht="51">
-      <c r="A18" s="98"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="98"/>
-      <c r="F18" s="95"/>
+    <row r="18" spans="1:24" ht="52.8">
+      <c r="A18" s="83"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="79"/>
       <c r="G18" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="H18" s="97"/>
+      <c r="H18" s="89"/>
       <c r="I18" s="55" t="s">
         <v>137</v>
       </c>
-      <c r="J18" s="93"/>
-      <c r="K18" s="93"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="93"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
       <c r="Q18" s="22"/>
@@ -4643,25 +4703,25 @@
       <c r="W18" s="22"/>
       <c r="X18" s="22"/>
     </row>
-    <row r="19" spans="1:24" ht="64.5" thickBot="1">
-      <c r="A19" s="98"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="98"/>
-      <c r="E19" s="98"/>
-      <c r="F19" s="96"/>
+    <row r="19" spans="1:24" ht="66.599999999999994" thickBot="1">
+      <c r="A19" s="83"/>
+      <c r="B19" s="83"/>
+      <c r="C19" s="83"/>
+      <c r="D19" s="83"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="80"/>
       <c r="G19" s="48" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="97"/>
+      <c r="H19" s="89"/>
       <c r="I19" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="93"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
       <c r="O19" s="22"/>
       <c r="P19" s="22"/>
       <c r="Q19" s="22"/>
@@ -4673,7 +4733,7 @@
       <c r="W19" s="22"/>
       <c r="X19" s="22"/>
     </row>
-    <row r="20" spans="1:24" ht="63.75">
+    <row r="20" spans="1:24" ht="66">
       <c r="A20" s="50">
         <v>3</v>
       </c>
@@ -4689,13 +4749,13 @@
       <c r="E20" s="21">
         <v>3</v>
       </c>
-      <c r="F20" s="94" t="s">
+      <c r="F20" s="78" t="s">
         <v>84</v>
       </c>
       <c r="G20" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="H20" s="105" t="s">
+      <c r="H20" s="81" t="s">
         <v>144</v>
       </c>
       <c r="I20" s="49" t="s">
@@ -4711,47 +4771,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="1:24" ht="63.75">
-      <c r="A21" s="98"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="95"/>
+    <row r="21" spans="1:24" ht="52.8">
+      <c r="A21" s="83"/>
+      <c r="B21" s="83"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="83"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="79"/>
       <c r="G21" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="H21" s="105"/>
+      <c r="H21" s="81"/>
       <c r="I21" s="55" t="s">
         <v>143</v>
       </c>
-      <c r="J21" s="93"/>
-      <c r="K21" s="93"/>
-      <c r="L21" s="93"/>
-      <c r="M21" s="93"/>
-      <c r="N21" s="93"/>
-    </row>
-    <row r="22" spans="1:24" ht="51.75" thickBot="1">
-      <c r="A22" s="98"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="96"/>
+      <c r="J21" s="84"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="84"/>
+    </row>
+    <row r="22" spans="1:24" ht="53.4" thickBot="1">
+      <c r="A22" s="83"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="83"/>
+      <c r="D22" s="83"/>
+      <c r="E22" s="83"/>
+      <c r="F22" s="80"/>
       <c r="G22" s="48" t="s">
         <v>141</v>
       </c>
-      <c r="H22" s="105"/>
+      <c r="H22" s="81"/>
       <c r="I22" s="56" t="s">
         <v>145</v>
       </c>
-      <c r="J22" s="93"/>
-      <c r="K22" s="93"/>
-      <c r="L22" s="93"/>
-      <c r="M22" s="93"/>
-      <c r="N22" s="93"/>
-    </row>
-    <row r="23" spans="1:24" ht="51">
+      <c r="J22" s="84"/>
+      <c r="K22" s="84"/>
+      <c r="L22" s="84"/>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+    </row>
+    <row r="23" spans="1:24" ht="52.8">
       <c r="A23" s="50">
         <v>3</v>
       </c>
@@ -4767,13 +4827,13 @@
       <c r="E23" s="21">
         <v>4</v>
       </c>
-      <c r="F23" s="94" t="s">
+      <c r="F23" s="78" t="s">
         <v>121</v>
       </c>
       <c r="G23" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="H23" s="105"/>
+      <c r="H23" s="81"/>
       <c r="I23" s="49" t="s">
         <v>149</v>
       </c>
@@ -4787,47 +4847,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="51">
-      <c r="A24" s="98"/>
-      <c r="B24" s="98"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="98"/>
-      <c r="E24" s="98"/>
-      <c r="F24" s="95"/>
+    <row r="24" spans="1:24" ht="52.8">
+      <c r="A24" s="83"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="83"/>
+      <c r="D24" s="83"/>
+      <c r="E24" s="83"/>
+      <c r="F24" s="79"/>
       <c r="G24" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="H24" s="105"/>
+      <c r="H24" s="81"/>
       <c r="I24" s="55" t="s">
         <v>150</v>
       </c>
-      <c r="J24" s="93"/>
-      <c r="K24" s="93"/>
-      <c r="L24" s="93"/>
-      <c r="M24" s="93"/>
-      <c r="N24" s="93"/>
-    </row>
-    <row r="25" spans="1:24" ht="64.5" thickBot="1">
-      <c r="A25" s="98"/>
-      <c r="B25" s="98"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="98"/>
-      <c r="E25" s="98"/>
-      <c r="F25" s="96"/>
+      <c r="J24" s="84"/>
+      <c r="K24" s="84"/>
+      <c r="L24" s="84"/>
+      <c r="M24" s="84"/>
+      <c r="N24" s="84"/>
+    </row>
+    <row r="25" spans="1:24" ht="66.599999999999994" thickBot="1">
+      <c r="A25" s="83"/>
+      <c r="B25" s="83"/>
+      <c r="C25" s="83"/>
+      <c r="D25" s="83"/>
+      <c r="E25" s="83"/>
+      <c r="F25" s="80"/>
       <c r="G25" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="H25" s="105"/>
+      <c r="H25" s="81"/>
       <c r="I25" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="J25" s="93"/>
-      <c r="K25" s="93"/>
-      <c r="L25" s="93"/>
-      <c r="M25" s="93"/>
-      <c r="N25" s="93"/>
-    </row>
-    <row r="26" spans="1:24" ht="63.75">
+      <c r="J25" s="84"/>
+      <c r="K25" s="84"/>
+      <c r="L25" s="84"/>
+      <c r="M25" s="84"/>
+      <c r="N25" s="84"/>
+    </row>
+    <row r="26" spans="1:24" ht="66">
       <c r="A26" s="50">
         <v>4</v>
       </c>
@@ -4843,13 +4903,13 @@
       <c r="E26" s="21">
         <v>5</v>
       </c>
-      <c r="F26" s="94" t="s">
+      <c r="F26" s="78" t="s">
         <v>85</v>
       </c>
       <c r="G26" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="H26" s="105" t="s">
+      <c r="H26" s="81" t="s">
         <v>155</v>
       </c>
       <c r="I26" s="49" t="s">
@@ -4865,47 +4925,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="63.75">
-      <c r="A27" s="98"/>
-      <c r="B27" s="98"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="98"/>
-      <c r="E27" s="98"/>
-      <c r="F27" s="95"/>
+    <row r="27" spans="1:24" ht="66">
+      <c r="A27" s="83"/>
+      <c r="B27" s="83"/>
+      <c r="C27" s="83"/>
+      <c r="D27" s="83"/>
+      <c r="E27" s="83"/>
+      <c r="F27" s="79"/>
       <c r="G27" s="47" t="s">
         <v>153</v>
       </c>
-      <c r="H27" s="105"/>
+      <c r="H27" s="81"/>
       <c r="I27" s="55" t="s">
         <v>157</v>
       </c>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="93"/>
-    </row>
-    <row r="28" spans="1:24" ht="64.5" thickBot="1">
-      <c r="A28" s="98"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="98"/>
-      <c r="E28" s="98"/>
-      <c r="F28" s="96"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="84"/>
+      <c r="L27" s="84"/>
+      <c r="M27" s="84"/>
+      <c r="N27" s="84"/>
+    </row>
+    <row r="28" spans="1:24" ht="66.599999999999994" thickBot="1">
+      <c r="A28" s="83"/>
+      <c r="B28" s="83"/>
+      <c r="C28" s="83"/>
+      <c r="D28" s="83"/>
+      <c r="E28" s="83"/>
+      <c r="F28" s="80"/>
       <c r="G28" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="105"/>
+      <c r="H28" s="81"/>
       <c r="I28" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="J28" s="93"/>
-      <c r="K28" s="93"/>
-      <c r="L28" s="93"/>
-      <c r="M28" s="93"/>
-      <c r="N28" s="93"/>
-    </row>
-    <row r="29" spans="1:24" ht="76.5">
+      <c r="J28" s="84"/>
+      <c r="K28" s="84"/>
+      <c r="L28" s="84"/>
+      <c r="M28" s="84"/>
+      <c r="N28" s="84"/>
+    </row>
+    <row r="29" spans="1:24" ht="79.2">
       <c r="A29" s="50">
         <v>4</v>
       </c>
@@ -4921,13 +4981,13 @@
       <c r="E29" s="21">
         <v>6</v>
       </c>
-      <c r="F29" s="94" t="s">
+      <c r="F29" s="78" t="s">
         <v>86</v>
       </c>
       <c r="G29" s="46" t="s">
         <v>159</v>
       </c>
-      <c r="H29" s="105" t="s">
+      <c r="H29" s="81" t="s">
         <v>162</v>
       </c>
       <c r="I29" s="49" t="s">
@@ -4943,47 +5003,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="63.75">
-      <c r="A30" s="98"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="98"/>
-      <c r="E30" s="98"/>
-      <c r="F30" s="95"/>
+    <row r="30" spans="1:24" ht="66">
+      <c r="A30" s="83"/>
+      <c r="B30" s="83"/>
+      <c r="C30" s="83"/>
+      <c r="D30" s="83"/>
+      <c r="E30" s="83"/>
+      <c r="F30" s="79"/>
       <c r="G30" s="47" t="s">
         <v>161</v>
       </c>
-      <c r="H30" s="105"/>
+      <c r="H30" s="81"/>
       <c r="I30" s="55" t="s">
         <v>164</v>
       </c>
-      <c r="J30" s="93"/>
-      <c r="K30" s="93"/>
-      <c r="L30" s="93"/>
-      <c r="M30" s="93"/>
-      <c r="N30" s="93"/>
-    </row>
-    <row r="31" spans="1:24" ht="77.25" thickBot="1">
-      <c r="A31" s="98"/>
-      <c r="B31" s="98"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="96"/>
+      <c r="J30" s="84"/>
+      <c r="K30" s="84"/>
+      <c r="L30" s="84"/>
+      <c r="M30" s="84"/>
+      <c r="N30" s="84"/>
+    </row>
+    <row r="31" spans="1:24" ht="79.8" thickBot="1">
+      <c r="A31" s="83"/>
+      <c r="B31" s="83"/>
+      <c r="C31" s="83"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="80"/>
       <c r="G31" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="H31" s="105"/>
+      <c r="H31" s="81"/>
       <c r="I31" s="56" t="s">
         <v>165</v>
       </c>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
-      <c r="L31" s="93"/>
-      <c r="M31" s="93"/>
-      <c r="N31" s="93"/>
-    </row>
-    <row r="32" spans="1:24" ht="38.25">
+      <c r="J31" s="84"/>
+      <c r="K31" s="84"/>
+      <c r="L31" s="84"/>
+      <c r="M31" s="84"/>
+      <c r="N31" s="84"/>
+    </row>
+    <row r="32" spans="1:24" ht="39.6">
       <c r="A32" s="50">
         <v>5</v>
       </c>
@@ -4999,13 +5059,13 @@
       <c r="E32" s="21">
         <v>7</v>
       </c>
-      <c r="F32" s="94" t="s">
+      <c r="F32" s="78" t="s">
         <v>122</v>
       </c>
       <c r="G32" s="46" t="s">
         <v>166</v>
       </c>
-      <c r="H32" s="105"/>
+      <c r="H32" s="81"/>
       <c r="I32" s="49" t="s">
         <v>169</v>
       </c>
@@ -5019,47 +5079,47 @@
         <v>120</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="38.25">
-      <c r="A33" s="98"/>
-      <c r="B33" s="98"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="98"/>
-      <c r="E33" s="98"/>
-      <c r="F33" s="95"/>
+    <row r="33" spans="1:14" ht="39.6">
+      <c r="A33" s="83"/>
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="79"/>
       <c r="G33" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="H33" s="105"/>
+      <c r="H33" s="81"/>
       <c r="I33" s="55" t="s">
         <v>170</v>
       </c>
-      <c r="J33" s="103"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="104"/>
-      <c r="N33" s="104"/>
-    </row>
-    <row r="34" spans="1:14" ht="51.75" thickBot="1">
-      <c r="A34" s="98"/>
-      <c r="B34" s="98"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="98"/>
-      <c r="E34" s="98"/>
-      <c r="F34" s="96"/>
+      <c r="J33" s="85"/>
+      <c r="K33" s="86"/>
+      <c r="L33" s="86"/>
+      <c r="M33" s="86"/>
+      <c r="N33" s="86"/>
+    </row>
+    <row r="34" spans="1:14" ht="53.4" thickBot="1">
+      <c r="A34" s="83"/>
+      <c r="B34" s="83"/>
+      <c r="C34" s="83"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="83"/>
+      <c r="F34" s="80"/>
       <c r="G34" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="H34" s="105"/>
+      <c r="H34" s="81"/>
       <c r="I34" s="56" t="s">
         <v>171</v>
       </c>
-      <c r="J34" s="104"/>
-      <c r="K34" s="104"/>
-      <c r="L34" s="104"/>
-      <c r="M34" s="104"/>
-      <c r="N34" s="104"/>
-    </row>
-    <row r="35" spans="1:14" ht="63.75">
+      <c r="J34" s="86"/>
+      <c r="K34" s="86"/>
+      <c r="L34" s="86"/>
+      <c r="M34" s="86"/>
+      <c r="N34" s="86"/>
+    </row>
+    <row r="35" spans="1:14" ht="66">
       <c r="A35" s="50">
         <v>5</v>
       </c>
@@ -5075,13 +5135,13 @@
       <c r="E35" s="21">
         <v>8</v>
       </c>
-      <c r="F35" s="94" t="s">
+      <c r="F35" s="78" t="s">
         <v>123</v>
       </c>
       <c r="G35" s="46" t="s">
         <v>172</v>
       </c>
-      <c r="H35" s="105"/>
+      <c r="H35" s="81"/>
       <c r="I35" s="49" t="s">
         <v>175</v>
       </c>
@@ -5095,47 +5155,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="63.75">
-      <c r="A36" s="98"/>
-      <c r="B36" s="98"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="98"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="95"/>
+    <row r="36" spans="1:14" ht="66">
+      <c r="A36" s="83"/>
+      <c r="B36" s="83"/>
+      <c r="C36" s="83"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="79"/>
       <c r="G36" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="H36" s="105"/>
+      <c r="H36" s="81"/>
       <c r="I36" s="55" t="s">
         <v>176</v>
       </c>
-      <c r="J36" s="93"/>
-      <c r="K36" s="93"/>
-      <c r="L36" s="93"/>
-      <c r="M36" s="93"/>
-      <c r="N36" s="93"/>
-    </row>
-    <row r="37" spans="1:14" ht="64.5" thickBot="1">
-      <c r="A37" s="98"/>
-      <c r="B37" s="98"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="98"/>
-      <c r="E37" s="98"/>
-      <c r="F37" s="96"/>
+      <c r="J36" s="84"/>
+      <c r="K36" s="84"/>
+      <c r="L36" s="84"/>
+      <c r="M36" s="84"/>
+      <c r="N36" s="84"/>
+    </row>
+    <row r="37" spans="1:14" ht="66.599999999999994" thickBot="1">
+      <c r="A37" s="83"/>
+      <c r="B37" s="83"/>
+      <c r="C37" s="83"/>
+      <c r="D37" s="83"/>
+      <c r="E37" s="83"/>
+      <c r="F37" s="80"/>
       <c r="G37" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="H37" s="105"/>
+      <c r="H37" s="81"/>
       <c r="I37" s="56" t="s">
         <v>177</v>
       </c>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="93"/>
-      <c r="M37" s="93"/>
-      <c r="N37" s="93"/>
-    </row>
-    <row r="38" spans="1:14" ht="51">
+      <c r="J37" s="84"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="84"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
+    </row>
+    <row r="38" spans="1:14" ht="52.8">
       <c r="A38" s="50">
         <v>3</v>
       </c>
@@ -5151,13 +5211,13 @@
       <c r="E38" s="21">
         <v>9</v>
       </c>
-      <c r="F38" s="94" t="s">
+      <c r="F38" s="78" t="s">
         <v>87</v>
       </c>
       <c r="G38" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="H38" s="105" t="s">
+      <c r="H38" s="81" t="s">
         <v>181</v>
       </c>
       <c r="I38" s="49" t="s">
@@ -5173,47 +5233,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="51">
-      <c r="A39" s="98"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="98"/>
-      <c r="E39" s="98"/>
-      <c r="F39" s="95"/>
+    <row r="39" spans="1:14" ht="52.8">
+      <c r="A39" s="83"/>
+      <c r="B39" s="83"/>
+      <c r="C39" s="83"/>
+      <c r="D39" s="83"/>
+      <c r="E39" s="83"/>
+      <c r="F39" s="79"/>
       <c r="G39" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="H39" s="105"/>
+      <c r="H39" s="81"/>
       <c r="I39" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="93"/>
-      <c r="L39" s="93"/>
-      <c r="M39" s="93"/>
-      <c r="N39" s="93"/>
-    </row>
-    <row r="40" spans="1:14" ht="51.75" thickBot="1">
-      <c r="A40" s="98"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="98"/>
-      <c r="E40" s="98"/>
-      <c r="F40" s="96"/>
+      <c r="J39" s="84"/>
+      <c r="K39" s="84"/>
+      <c r="L39" s="84"/>
+      <c r="M39" s="84"/>
+      <c r="N39" s="84"/>
+    </row>
+    <row r="40" spans="1:14" ht="53.4" thickBot="1">
+      <c r="A40" s="83"/>
+      <c r="B40" s="83"/>
+      <c r="C40" s="83"/>
+      <c r="D40" s="83"/>
+      <c r="E40" s="83"/>
+      <c r="F40" s="80"/>
       <c r="G40" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="H40" s="105"/>
+      <c r="H40" s="81"/>
       <c r="I40" s="56" t="s">
         <v>184</v>
       </c>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93"/>
-      <c r="L40" s="93"/>
-      <c r="M40" s="93"/>
-      <c r="N40" s="93"/>
-    </row>
-    <row r="41" spans="1:14" ht="63.75">
+      <c r="J40" s="84"/>
+      <c r="K40" s="84"/>
+      <c r="L40" s="84"/>
+      <c r="M40" s="84"/>
+      <c r="N40" s="84"/>
+    </row>
+    <row r="41" spans="1:14" ht="52.8">
       <c r="A41" s="50">
         <v>3</v>
       </c>
@@ -5229,13 +5289,13 @@
       <c r="E41" s="21">
         <v>10</v>
       </c>
-      <c r="F41" s="94" t="s">
+      <c r="F41" s="78" t="s">
         <v>88</v>
       </c>
       <c r="G41" s="46" t="s">
         <v>185</v>
       </c>
-      <c r="H41" s="105" t="s">
+      <c r="H41" s="81" t="s">
         <v>188</v>
       </c>
       <c r="I41" s="49" t="s">
@@ -5251,47 +5311,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="51">
-      <c r="A42" s="98"/>
-      <c r="B42" s="98"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="98"/>
-      <c r="E42" s="98"/>
-      <c r="F42" s="95"/>
+    <row r="42" spans="1:14" ht="52.8">
+      <c r="A42" s="83"/>
+      <c r="B42" s="83"/>
+      <c r="C42" s="83"/>
+      <c r="D42" s="83"/>
+      <c r="E42" s="83"/>
+      <c r="F42" s="79"/>
       <c r="G42" s="47" t="s">
         <v>186</v>
       </c>
-      <c r="H42" s="105"/>
+      <c r="H42" s="81"/>
       <c r="I42" s="55" t="s">
         <v>190</v>
       </c>
-      <c r="J42" s="93"/>
-      <c r="K42" s="93"/>
-      <c r="L42" s="93"/>
-      <c r="M42" s="93"/>
-      <c r="N42" s="93"/>
-    </row>
-    <row r="43" spans="1:14" ht="51.75" thickBot="1">
-      <c r="A43" s="98"/>
-      <c r="B43" s="98"/>
-      <c r="C43" s="98"/>
-      <c r="D43" s="98"/>
-      <c r="E43" s="98"/>
-      <c r="F43" s="96"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="84"/>
+      <c r="M42" s="84"/>
+      <c r="N42" s="84"/>
+    </row>
+    <row r="43" spans="1:14" ht="53.4" thickBot="1">
+      <c r="A43" s="83"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="80"/>
       <c r="G43" s="48" t="s">
         <v>187</v>
       </c>
-      <c r="H43" s="105"/>
+      <c r="H43" s="81"/>
       <c r="I43" s="56" t="s">
         <v>191</v>
       </c>
-      <c r="J43" s="93"/>
-      <c r="K43" s="93"/>
-      <c r="L43" s="93"/>
-      <c r="M43" s="93"/>
-      <c r="N43" s="93"/>
-    </row>
-    <row r="44" spans="1:14" ht="63.75">
+      <c r="J43" s="84"/>
+      <c r="K43" s="84"/>
+      <c r="L43" s="84"/>
+      <c r="M43" s="84"/>
+      <c r="N43" s="84"/>
+    </row>
+    <row r="44" spans="1:14" ht="52.8">
       <c r="A44" s="50">
         <v>3</v>
       </c>
@@ -5307,13 +5367,13 @@
       <c r="E44" s="21">
         <v>11</v>
       </c>
-      <c r="F44" s="94" t="s">
+      <c r="F44" s="78" t="s">
         <v>89</v>
       </c>
       <c r="G44" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="H44" s="105" t="s">
+      <c r="H44" s="81" t="s">
         <v>195</v>
       </c>
       <c r="I44" s="49" t="s">
@@ -5329,47 +5389,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="38.25">
-      <c r="A45" s="98"/>
-      <c r="B45" s="98"/>
-      <c r="C45" s="98"/>
-      <c r="D45" s="98"/>
-      <c r="E45" s="98"/>
-      <c r="F45" s="95"/>
+    <row r="45" spans="1:14" ht="39.6">
+      <c r="A45" s="83"/>
+      <c r="B45" s="83"/>
+      <c r="C45" s="83"/>
+      <c r="D45" s="83"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="79"/>
       <c r="G45" s="47" t="s">
         <v>193</v>
       </c>
-      <c r="H45" s="105"/>
+      <c r="H45" s="81"/>
       <c r="I45" s="55" t="s">
         <v>197</v>
       </c>
-      <c r="J45" s="93"/>
-      <c r="K45" s="93"/>
-      <c r="L45" s="93"/>
-      <c r="M45" s="93"/>
-      <c r="N45" s="93"/>
-    </row>
-    <row r="46" spans="1:14" ht="51.75" thickBot="1">
-      <c r="A46" s="98"/>
-      <c r="B46" s="98"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="98"/>
-      <c r="E46" s="98"/>
-      <c r="F46" s="96"/>
+      <c r="J45" s="84"/>
+      <c r="K45" s="84"/>
+      <c r="L45" s="84"/>
+      <c r="M45" s="84"/>
+      <c r="N45" s="84"/>
+    </row>
+    <row r="46" spans="1:14" ht="53.4" thickBot="1">
+      <c r="A46" s="83"/>
+      <c r="B46" s="83"/>
+      <c r="C46" s="83"/>
+      <c r="D46" s="83"/>
+      <c r="E46" s="83"/>
+      <c r="F46" s="80"/>
       <c r="G46" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="H46" s="105"/>
+      <c r="H46" s="81"/>
       <c r="I46" s="56" t="s">
         <v>198</v>
       </c>
-      <c r="J46" s="93"/>
-      <c r="K46" s="93"/>
-      <c r="L46" s="93"/>
-      <c r="M46" s="93"/>
-      <c r="N46" s="93"/>
-    </row>
-    <row r="47" spans="1:14" ht="51">
+      <c r="J46" s="84"/>
+      <c r="K46" s="84"/>
+      <c r="L46" s="84"/>
+      <c r="M46" s="84"/>
+      <c r="N46" s="84"/>
+    </row>
+    <row r="47" spans="1:14" ht="52.8">
       <c r="A47" s="50">
         <v>6</v>
       </c>
@@ -5385,13 +5445,13 @@
       <c r="E47" s="21">
         <v>12</v>
       </c>
-      <c r="F47" s="94" t="s">
+      <c r="F47" s="78" t="s">
         <v>90</v>
       </c>
       <c r="G47" s="46" t="s">
         <v>199</v>
       </c>
-      <c r="H47" s="105" t="s">
+      <c r="H47" s="81" t="s">
         <v>201</v>
       </c>
       <c r="I47" s="49" t="s">
@@ -5407,47 +5467,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="63.75">
-      <c r="A48" s="98"/>
-      <c r="B48" s="98"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="98"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="95"/>
+    <row r="48" spans="1:14" ht="66">
+      <c r="A48" s="83"/>
+      <c r="B48" s="83"/>
+      <c r="C48" s="83"/>
+      <c r="D48" s="83"/>
+      <c r="E48" s="83"/>
+      <c r="F48" s="79"/>
       <c r="G48" s="47" t="s">
         <v>200</v>
       </c>
-      <c r="H48" s="105"/>
+      <c r="H48" s="81"/>
       <c r="I48" s="55" t="s">
         <v>203</v>
       </c>
-      <c r="J48" s="93"/>
-      <c r="K48" s="93"/>
-      <c r="L48" s="93"/>
-      <c r="M48" s="93"/>
-      <c r="N48" s="93"/>
-    </row>
-    <row r="49" spans="1:14" ht="64.5" thickBot="1">
-      <c r="A49" s="98"/>
-      <c r="B49" s="98"/>
-      <c r="C49" s="98"/>
-      <c r="D49" s="98"/>
-      <c r="E49" s="98"/>
-      <c r="F49" s="96"/>
+      <c r="J48" s="84"/>
+      <c r="K48" s="84"/>
+      <c r="L48" s="84"/>
+      <c r="M48" s="84"/>
+      <c r="N48" s="84"/>
+    </row>
+    <row r="49" spans="1:14" ht="66.599999999999994" thickBot="1">
+      <c r="A49" s="83"/>
+      <c r="B49" s="83"/>
+      <c r="C49" s="83"/>
+      <c r="D49" s="83"/>
+      <c r="E49" s="83"/>
+      <c r="F49" s="80"/>
       <c r="G49" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="H49" s="105"/>
+      <c r="H49" s="81"/>
       <c r="I49" s="56" t="s">
         <v>204</v>
       </c>
-      <c r="J49" s="93"/>
-      <c r="K49" s="93"/>
-      <c r="L49" s="93"/>
-      <c r="M49" s="93"/>
-      <c r="N49" s="93"/>
-    </row>
-    <row r="50" spans="1:14" ht="76.5">
+      <c r="J49" s="84"/>
+      <c r="K49" s="84"/>
+      <c r="L49" s="84"/>
+      <c r="M49" s="84"/>
+      <c r="N49" s="84"/>
+    </row>
+    <row r="50" spans="1:14" ht="79.2">
       <c r="A50" s="50">
         <v>7</v>
       </c>
@@ -5463,13 +5523,13 @@
       <c r="E50" s="21">
         <v>13</v>
       </c>
-      <c r="F50" s="94" t="s">
+      <c r="F50" s="78" t="s">
         <v>91</v>
       </c>
       <c r="G50" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="H50" s="105" t="s">
+      <c r="H50" s="81" t="s">
         <v>208</v>
       </c>
       <c r="I50" s="49" t="s">
@@ -5485,47 +5545,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="76.5">
-      <c r="A51" s="98"/>
-      <c r="B51" s="98"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="98"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="95"/>
+    <row r="51" spans="1:14" ht="79.2">
+      <c r="A51" s="83"/>
+      <c r="B51" s="83"/>
+      <c r="C51" s="83"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="79"/>
       <c r="G51" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="H51" s="105"/>
+      <c r="H51" s="81"/>
       <c r="I51" s="55" t="s">
         <v>210</v>
       </c>
-      <c r="J51" s="93"/>
-      <c r="K51" s="93"/>
-      <c r="L51" s="93"/>
-      <c r="M51" s="93"/>
-      <c r="N51" s="93"/>
-    </row>
-    <row r="52" spans="1:14" ht="77.25" thickBot="1">
-      <c r="A52" s="98"/>
-      <c r="B52" s="98"/>
-      <c r="C52" s="98"/>
-      <c r="D52" s="98"/>
-      <c r="E52" s="98"/>
-      <c r="F52" s="96"/>
+      <c r="J51" s="84"/>
+      <c r="K51" s="84"/>
+      <c r="L51" s="84"/>
+      <c r="M51" s="84"/>
+      <c r="N51" s="84"/>
+    </row>
+    <row r="52" spans="1:14" ht="66.599999999999994" thickBot="1">
+      <c r="A52" s="83"/>
+      <c r="B52" s="83"/>
+      <c r="C52" s="83"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="80"/>
       <c r="G52" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="H52" s="105"/>
+      <c r="H52" s="81"/>
       <c r="I52" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="J52" s="93"/>
-      <c r="K52" s="93"/>
-      <c r="L52" s="93"/>
-      <c r="M52" s="93"/>
-      <c r="N52" s="93"/>
-    </row>
-    <row r="53" spans="1:14" ht="63.75">
+      <c r="J52" s="84"/>
+      <c r="K52" s="84"/>
+      <c r="L52" s="84"/>
+      <c r="M52" s="84"/>
+      <c r="N52" s="84"/>
+    </row>
+    <row r="53" spans="1:14" ht="66">
       <c r="A53" s="50">
         <v>8</v>
       </c>
@@ -5541,13 +5601,13 @@
       <c r="E53" s="21">
         <v>14</v>
       </c>
-      <c r="F53" s="94" t="s">
+      <c r="F53" s="78" t="s">
         <v>92</v>
       </c>
       <c r="G53" s="46" t="s">
         <v>212</v>
       </c>
-      <c r="H53" s="105" t="s">
+      <c r="H53" s="81" t="s">
         <v>215</v>
       </c>
       <c r="I53" s="49" t="s">
@@ -5563,47 +5623,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="51">
-      <c r="A54" s="98"/>
-      <c r="B54" s="98"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="98"/>
-      <c r="E54" s="98"/>
-      <c r="F54" s="95"/>
+    <row r="54" spans="1:14" ht="52.8">
+      <c r="A54" s="83"/>
+      <c r="B54" s="83"/>
+      <c r="C54" s="83"/>
+      <c r="D54" s="83"/>
+      <c r="E54" s="83"/>
+      <c r="F54" s="79"/>
       <c r="G54" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="H54" s="105"/>
+      <c r="H54" s="81"/>
       <c r="I54" s="55" t="s">
         <v>217</v>
       </c>
-      <c r="J54" s="93"/>
-      <c r="K54" s="93"/>
-      <c r="L54" s="93"/>
-      <c r="M54" s="93"/>
-      <c r="N54" s="93"/>
-    </row>
-    <row r="55" spans="1:14" ht="77.25" thickBot="1">
-      <c r="A55" s="98"/>
-      <c r="B55" s="98"/>
-      <c r="C55" s="98"/>
-      <c r="D55" s="98"/>
-      <c r="E55" s="98"/>
-      <c r="F55" s="96"/>
+      <c r="J54" s="84"/>
+      <c r="K54" s="84"/>
+      <c r="L54" s="84"/>
+      <c r="M54" s="84"/>
+      <c r="N54" s="84"/>
+    </row>
+    <row r="55" spans="1:14" ht="79.8" thickBot="1">
+      <c r="A55" s="83"/>
+      <c r="B55" s="83"/>
+      <c r="C55" s="83"/>
+      <c r="D55" s="83"/>
+      <c r="E55" s="83"/>
+      <c r="F55" s="80"/>
       <c r="G55" s="48" t="s">
         <v>214</v>
       </c>
-      <c r="H55" s="105"/>
+      <c r="H55" s="81"/>
       <c r="I55" s="56" t="s">
         <v>218</v>
       </c>
-      <c r="J55" s="93"/>
-      <c r="K55" s="93"/>
-      <c r="L55" s="93"/>
-      <c r="M55" s="93"/>
-      <c r="N55" s="93"/>
-    </row>
-    <row r="56" spans="1:14" ht="51">
+      <c r="J55" s="84"/>
+      <c r="K55" s="84"/>
+      <c r="L55" s="84"/>
+      <c r="M55" s="84"/>
+      <c r="N55" s="84"/>
+    </row>
+    <row r="56" spans="1:14" ht="39.6">
       <c r="A56" s="50">
         <v>9</v>
       </c>
@@ -5619,13 +5679,13 @@
       <c r="E56" s="21">
         <v>15</v>
       </c>
-      <c r="F56" s="94" t="s">
+      <c r="F56" s="78" t="s">
         <v>124</v>
       </c>
       <c r="G56" s="46" t="s">
         <v>219</v>
       </c>
-      <c r="H56" s="105" t="s">
+      <c r="H56" s="81" t="s">
         <v>222</v>
       </c>
       <c r="I56" s="49" t="s">
@@ -5641,47 +5701,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="51">
-      <c r="A57" s="98"/>
-      <c r="B57" s="98"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="98"/>
-      <c r="E57" s="98"/>
-      <c r="F57" s="95"/>
+    <row r="57" spans="1:14" ht="52.8">
+      <c r="A57" s="83"/>
+      <c r="B57" s="83"/>
+      <c r="C57" s="83"/>
+      <c r="D57" s="83"/>
+      <c r="E57" s="83"/>
+      <c r="F57" s="79"/>
       <c r="G57" s="47" t="s">
         <v>220</v>
       </c>
-      <c r="H57" s="105"/>
+      <c r="H57" s="81"/>
       <c r="I57" s="55" t="s">
         <v>224</v>
       </c>
-      <c r="J57" s="93"/>
-      <c r="K57" s="93"/>
-      <c r="L57" s="93"/>
-      <c r="M57" s="93"/>
-      <c r="N57" s="93"/>
-    </row>
-    <row r="58" spans="1:14" ht="77.25" thickBot="1">
-      <c r="A58" s="98"/>
-      <c r="B58" s="98"/>
-      <c r="C58" s="98"/>
-      <c r="D58" s="98"/>
-      <c r="E58" s="98"/>
-      <c r="F58" s="96"/>
+      <c r="J57" s="84"/>
+      <c r="K57" s="84"/>
+      <c r="L57" s="84"/>
+      <c r="M57" s="84"/>
+      <c r="N57" s="84"/>
+    </row>
+    <row r="58" spans="1:14" ht="79.8" thickBot="1">
+      <c r="A58" s="83"/>
+      <c r="B58" s="83"/>
+      <c r="C58" s="83"/>
+      <c r="D58" s="83"/>
+      <c r="E58" s="83"/>
+      <c r="F58" s="80"/>
       <c r="G58" s="48" t="s">
         <v>221</v>
       </c>
-      <c r="H58" s="105"/>
+      <c r="H58" s="81"/>
       <c r="I58" s="56" t="s">
         <v>225</v>
       </c>
-      <c r="J58" s="93"/>
-      <c r="K58" s="93"/>
-      <c r="L58" s="93"/>
-      <c r="M58" s="93"/>
-      <c r="N58" s="93"/>
-    </row>
-    <row r="59" spans="1:14" ht="38.25">
+      <c r="J58" s="84"/>
+      <c r="K58" s="84"/>
+      <c r="L58" s="84"/>
+      <c r="M58" s="84"/>
+      <c r="N58" s="84"/>
+    </row>
+    <row r="59" spans="1:14" ht="39.6">
       <c r="A59" s="50">
         <v>2</v>
       </c>
@@ -5697,13 +5757,13 @@
       <c r="E59" s="21">
         <v>16</v>
       </c>
-      <c r="F59" s="94" t="s">
+      <c r="F59" s="78" t="s">
         <v>93</v>
       </c>
       <c r="G59" s="46" t="s">
         <v>226</v>
       </c>
-      <c r="H59" s="105" t="s">
+      <c r="H59" s="81" t="s">
         <v>246</v>
       </c>
       <c r="I59" s="49" t="s">
@@ -5719,47 +5779,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="51">
-      <c r="A60" s="98"/>
-      <c r="B60" s="98"/>
-      <c r="C60" s="98"/>
-      <c r="D60" s="98"/>
-      <c r="E60" s="98"/>
-      <c r="F60" s="95"/>
+    <row r="60" spans="1:14" ht="52.8">
+      <c r="A60" s="83"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="83"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="79"/>
       <c r="G60" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="H60" s="105"/>
+      <c r="H60" s="81"/>
       <c r="I60" s="55" t="s">
         <v>230</v>
       </c>
-      <c r="J60" s="93"/>
-      <c r="K60" s="93"/>
-      <c r="L60" s="93"/>
-      <c r="M60" s="93"/>
-      <c r="N60" s="93"/>
-    </row>
-    <row r="61" spans="1:14" ht="64.5" thickBot="1">
-      <c r="A61" s="98"/>
-      <c r="B61" s="98"/>
-      <c r="C61" s="98"/>
-      <c r="D61" s="98"/>
-      <c r="E61" s="98"/>
-      <c r="F61" s="96"/>
+      <c r="J60" s="84"/>
+      <c r="K60" s="84"/>
+      <c r="L60" s="84"/>
+      <c r="M60" s="84"/>
+      <c r="N60" s="84"/>
+    </row>
+    <row r="61" spans="1:14" ht="66.599999999999994" thickBot="1">
+      <c r="A61" s="83"/>
+      <c r="B61" s="83"/>
+      <c r="C61" s="83"/>
+      <c r="D61" s="83"/>
+      <c r="E61" s="83"/>
+      <c r="F61" s="80"/>
       <c r="G61" s="48" t="s">
         <v>228</v>
       </c>
-      <c r="H61" s="105"/>
+      <c r="H61" s="81"/>
       <c r="I61" s="56" t="s">
         <v>231</v>
       </c>
-      <c r="J61" s="93"/>
-      <c r="K61" s="93"/>
-      <c r="L61" s="93"/>
-      <c r="M61" s="93"/>
-      <c r="N61" s="93"/>
-    </row>
-    <row r="62" spans="1:14" ht="38.25">
+      <c r="J61" s="84"/>
+      <c r="K61" s="84"/>
+      <c r="L61" s="84"/>
+      <c r="M61" s="84"/>
+      <c r="N61" s="84"/>
+    </row>
+    <row r="62" spans="1:14" ht="39.6">
       <c r="A62" s="50">
         <v>2</v>
       </c>
@@ -5775,13 +5835,13 @@
       <c r="E62" s="21">
         <v>17</v>
       </c>
-      <c r="F62" s="94" t="s">
+      <c r="F62" s="78" t="s">
         <v>94</v>
       </c>
       <c r="G62" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="H62" s="105" t="s">
+      <c r="H62" s="81" t="s">
         <v>245</v>
       </c>
       <c r="I62" s="49" t="s">
@@ -5797,47 +5857,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="63.75">
-      <c r="A63" s="98"/>
-      <c r="B63" s="98"/>
-      <c r="C63" s="98"/>
-      <c r="D63" s="98"/>
-      <c r="E63" s="98"/>
-      <c r="F63" s="95"/>
+    <row r="63" spans="1:14" ht="66">
+      <c r="A63" s="83"/>
+      <c r="B63" s="83"/>
+      <c r="C63" s="83"/>
+      <c r="D63" s="83"/>
+      <c r="E63" s="83"/>
+      <c r="F63" s="79"/>
       <c r="G63" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="H63" s="105"/>
+      <c r="H63" s="81"/>
       <c r="I63" s="55" t="s">
         <v>236</v>
       </c>
-      <c r="J63" s="93"/>
-      <c r="K63" s="93"/>
-      <c r="L63" s="93"/>
-      <c r="M63" s="93"/>
-      <c r="N63" s="93"/>
-    </row>
-    <row r="64" spans="1:14" ht="64.5" thickBot="1">
-      <c r="A64" s="98"/>
-      <c r="B64" s="98"/>
-      <c r="C64" s="98"/>
-      <c r="D64" s="98"/>
-      <c r="E64" s="98"/>
-      <c r="F64" s="96"/>
+      <c r="J63" s="84"/>
+      <c r="K63" s="84"/>
+      <c r="L63" s="84"/>
+      <c r="M63" s="84"/>
+      <c r="N63" s="84"/>
+    </row>
+    <row r="64" spans="1:14" ht="66.599999999999994" thickBot="1">
+      <c r="A64" s="83"/>
+      <c r="B64" s="83"/>
+      <c r="C64" s="83"/>
+      <c r="D64" s="83"/>
+      <c r="E64" s="83"/>
+      <c r="F64" s="80"/>
       <c r="G64" s="48" t="s">
         <v>234</v>
       </c>
-      <c r="H64" s="105"/>
+      <c r="H64" s="81"/>
       <c r="I64" s="56" t="s">
         <v>237</v>
       </c>
-      <c r="J64" s="93"/>
-      <c r="K64" s="93"/>
-      <c r="L64" s="93"/>
-      <c r="M64" s="93"/>
-      <c r="N64" s="93"/>
-    </row>
-    <row r="65" spans="1:14" ht="51">
+      <c r="J64" s="84"/>
+      <c r="K64" s="84"/>
+      <c r="L64" s="84"/>
+      <c r="M64" s="84"/>
+      <c r="N64" s="84"/>
+    </row>
+    <row r="65" spans="1:14" ht="52.8">
       <c r="A65" s="50">
         <v>2</v>
       </c>
@@ -5853,13 +5913,13 @@
       <c r="E65" s="21">
         <v>18</v>
       </c>
-      <c r="F65" s="94" t="s">
+      <c r="F65" s="78" t="s">
         <v>95</v>
       </c>
       <c r="G65" s="46" t="s">
         <v>238</v>
       </c>
-      <c r="H65" s="105" t="s">
+      <c r="H65" s="81" t="s">
         <v>244</v>
       </c>
       <c r="I65" s="49" t="s">
@@ -5875,47 +5935,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="63.75">
-      <c r="A66" s="98"/>
-      <c r="B66" s="98"/>
-      <c r="C66" s="98"/>
-      <c r="D66" s="98"/>
-      <c r="E66" s="98"/>
-      <c r="F66" s="95"/>
+    <row r="66" spans="1:14" ht="66">
+      <c r="A66" s="83"/>
+      <c r="B66" s="83"/>
+      <c r="C66" s="83"/>
+      <c r="D66" s="83"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="79"/>
       <c r="G66" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="H66" s="105"/>
+      <c r="H66" s="81"/>
       <c r="I66" s="55" t="s">
         <v>242</v>
       </c>
-      <c r="J66" s="93"/>
-      <c r="K66" s="93"/>
-      <c r="L66" s="93"/>
-      <c r="M66" s="93"/>
-      <c r="N66" s="93"/>
-    </row>
-    <row r="67" spans="1:14" ht="64.5" thickBot="1">
-      <c r="A67" s="98"/>
-      <c r="B67" s="98"/>
-      <c r="C67" s="98"/>
-      <c r="D67" s="98"/>
-      <c r="E67" s="98"/>
-      <c r="F67" s="96"/>
+      <c r="J66" s="84"/>
+      <c r="K66" s="84"/>
+      <c r="L66" s="84"/>
+      <c r="M66" s="84"/>
+      <c r="N66" s="84"/>
+    </row>
+    <row r="67" spans="1:14" ht="66.599999999999994" thickBot="1">
+      <c r="A67" s="83"/>
+      <c r="B67" s="83"/>
+      <c r="C67" s="83"/>
+      <c r="D67" s="83"/>
+      <c r="E67" s="83"/>
+      <c r="F67" s="80"/>
       <c r="G67" s="48" t="s">
         <v>240</v>
       </c>
-      <c r="H67" s="105"/>
+      <c r="H67" s="81"/>
       <c r="I67" s="56" t="s">
         <v>243</v>
       </c>
-      <c r="J67" s="93"/>
-      <c r="K67" s="93"/>
-      <c r="L67" s="93"/>
-      <c r="M67" s="93"/>
-      <c r="N67" s="93"/>
-    </row>
-    <row r="68" spans="1:14" ht="51">
+      <c r="J67" s="84"/>
+      <c r="K67" s="84"/>
+      <c r="L67" s="84"/>
+      <c r="M67" s="84"/>
+      <c r="N67" s="84"/>
+    </row>
+    <row r="68" spans="1:14" ht="52.8">
       <c r="A68" s="50">
         <v>2</v>
       </c>
@@ -5931,13 +5991,13 @@
       <c r="E68" s="21">
         <v>19</v>
       </c>
-      <c r="F68" s="94" t="s">
+      <c r="F68" s="78" t="s">
         <v>96</v>
       </c>
       <c r="G68" s="46" t="s">
         <v>247</v>
       </c>
-      <c r="H68" s="105" t="s">
+      <c r="H68" s="81" t="s">
         <v>250</v>
       </c>
       <c r="I68" s="49" t="s">
@@ -5953,49 +6013,49 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="63.75">
-      <c r="A69" s="106" t="s">
+    <row r="69" spans="1:14" ht="52.8">
+      <c r="A69" s="82" t="s">
         <v>109</v>
       </c>
-      <c r="B69" s="98"/>
-      <c r="C69" s="98"/>
-      <c r="D69" s="98"/>
-      <c r="E69" s="98"/>
-      <c r="F69" s="95"/>
+      <c r="B69" s="83"/>
+      <c r="C69" s="83"/>
+      <c r="D69" s="83"/>
+      <c r="E69" s="83"/>
+      <c r="F69" s="79"/>
       <c r="G69" s="47" t="s">
         <v>248</v>
       </c>
-      <c r="H69" s="105"/>
+      <c r="H69" s="81"/>
       <c r="I69" s="55" t="s">
         <v>252</v>
       </c>
-      <c r="J69" s="93"/>
-      <c r="K69" s="93"/>
-      <c r="L69" s="93"/>
-      <c r="M69" s="93"/>
-      <c r="N69" s="93"/>
-    </row>
-    <row r="70" spans="1:14" ht="77.25" thickBot="1">
-      <c r="A70" s="98"/>
-      <c r="B70" s="98"/>
-      <c r="C70" s="98"/>
-      <c r="D70" s="98"/>
-      <c r="E70" s="98"/>
-      <c r="F70" s="96"/>
+      <c r="J69" s="84"/>
+      <c r="K69" s="84"/>
+      <c r="L69" s="84"/>
+      <c r="M69" s="84"/>
+      <c r="N69" s="84"/>
+    </row>
+    <row r="70" spans="1:14" ht="79.8" thickBot="1">
+      <c r="A70" s="83"/>
+      <c r="B70" s="83"/>
+      <c r="C70" s="83"/>
+      <c r="D70" s="83"/>
+      <c r="E70" s="83"/>
+      <c r="F70" s="80"/>
       <c r="G70" s="48" t="s">
         <v>249</v>
       </c>
-      <c r="H70" s="105"/>
+      <c r="H70" s="81"/>
       <c r="I70" s="56" t="s">
         <v>253</v>
       </c>
-      <c r="J70" s="93"/>
-      <c r="K70" s="93"/>
-      <c r="L70" s="93"/>
-      <c r="M70" s="93"/>
-      <c r="N70" s="93"/>
-    </row>
-    <row r="71" spans="1:14" ht="38.25">
+      <c r="J70" s="84"/>
+      <c r="K70" s="84"/>
+      <c r="L70" s="84"/>
+      <c r="M70" s="84"/>
+      <c r="N70" s="84"/>
+    </row>
+    <row r="71" spans="1:14" ht="39.6">
       <c r="A71" s="50">
         <v>2</v>
       </c>
@@ -6011,13 +6071,13 @@
       <c r="E71" s="21">
         <v>20</v>
       </c>
-      <c r="F71" s="94" t="s">
+      <c r="F71" s="78" t="s">
         <v>97</v>
       </c>
       <c r="G71" s="46" t="s">
         <v>254</v>
       </c>
-      <c r="H71" s="105" t="s">
+      <c r="H71" s="81" t="s">
         <v>257</v>
       </c>
       <c r="I71" s="49" t="s">
@@ -6033,45 +6093,45 @@
         <v>68</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="51">
-      <c r="A72" s="98"/>
-      <c r="B72" s="98"/>
-      <c r="C72" s="98"/>
-      <c r="D72" s="98"/>
-      <c r="E72" s="98"/>
-      <c r="F72" s="95"/>
+    <row r="72" spans="1:14" ht="52.8">
+      <c r="A72" s="83"/>
+      <c r="B72" s="83"/>
+      <c r="C72" s="83"/>
+      <c r="D72" s="83"/>
+      <c r="E72" s="83"/>
+      <c r="F72" s="79"/>
       <c r="G72" s="47" t="s">
         <v>255</v>
       </c>
-      <c r="H72" s="105"/>
+      <c r="H72" s="81"/>
       <c r="I72" s="55" t="s">
         <v>259</v>
       </c>
-      <c r="J72" s="93"/>
-      <c r="K72" s="93"/>
-      <c r="L72" s="93"/>
-      <c r="M72" s="93"/>
-      <c r="N72" s="93"/>
-    </row>
-    <row r="73" spans="1:14" ht="77.25" thickBot="1">
-      <c r="A73" s="98"/>
-      <c r="B73" s="98"/>
-      <c r="C73" s="98"/>
-      <c r="D73" s="98"/>
-      <c r="E73" s="98"/>
-      <c r="F73" s="96"/>
+      <c r="J72" s="84"/>
+      <c r="K72" s="84"/>
+      <c r="L72" s="84"/>
+      <c r="M72" s="84"/>
+      <c r="N72" s="84"/>
+    </row>
+    <row r="73" spans="1:14" ht="79.8" thickBot="1">
+      <c r="A73" s="83"/>
+      <c r="B73" s="83"/>
+      <c r="C73" s="83"/>
+      <c r="D73" s="83"/>
+      <c r="E73" s="83"/>
+      <c r="F73" s="80"/>
       <c r="G73" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="H73" s="105"/>
+      <c r="H73" s="81"/>
       <c r="I73" s="56" t="s">
         <v>260</v>
       </c>
-      <c r="J73" s="93"/>
-      <c r="K73" s="93"/>
-      <c r="L73" s="93"/>
-      <c r="M73" s="93"/>
-      <c r="N73" s="93"/>
+      <c r="J73" s="84"/>
+      <c r="K73" s="84"/>
+      <c r="L73" s="84"/>
+      <c r="M73" s="84"/>
+      <c r="N73" s="84"/>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="22"/>
@@ -7061,88 +7121,6 @@
   </sheetData>
   <autoFilter ref="A12:N19" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <mergeCells count="98">
-    <mergeCell ref="F68:F70"/>
-    <mergeCell ref="H68:H70"/>
-    <mergeCell ref="A69:E70"/>
-    <mergeCell ref="J69:N70"/>
-    <mergeCell ref="F71:F73"/>
-    <mergeCell ref="H71:H73"/>
-    <mergeCell ref="A72:E73"/>
-    <mergeCell ref="J72:N73"/>
-    <mergeCell ref="F62:F64"/>
-    <mergeCell ref="H62:H64"/>
-    <mergeCell ref="A63:E64"/>
-    <mergeCell ref="J63:N64"/>
-    <mergeCell ref="F65:F67"/>
-    <mergeCell ref="H65:H67"/>
-    <mergeCell ref="A66:E67"/>
-    <mergeCell ref="J66:N67"/>
-    <mergeCell ref="F56:F58"/>
-    <mergeCell ref="H56:H58"/>
-    <mergeCell ref="A57:E58"/>
-    <mergeCell ref="J57:N58"/>
-    <mergeCell ref="F59:F61"/>
-    <mergeCell ref="H59:H61"/>
-    <mergeCell ref="A60:E61"/>
-    <mergeCell ref="J60:N61"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="A51:E52"/>
-    <mergeCell ref="J51:N52"/>
-    <mergeCell ref="F53:F55"/>
-    <mergeCell ref="H53:H55"/>
-    <mergeCell ref="A54:E55"/>
-    <mergeCell ref="J54:N55"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="A45:E46"/>
-    <mergeCell ref="J45:N46"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="H47:H49"/>
-    <mergeCell ref="A48:E49"/>
-    <mergeCell ref="J48:N49"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="H38:H40"/>
-    <mergeCell ref="A39:E40"/>
-    <mergeCell ref="J39:N40"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="A42:E43"/>
-    <mergeCell ref="J42:N43"/>
-    <mergeCell ref="F32:F34"/>
-    <mergeCell ref="H32:H34"/>
-    <mergeCell ref="A33:E34"/>
-    <mergeCell ref="J33:N34"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="H35:H37"/>
-    <mergeCell ref="A36:E37"/>
-    <mergeCell ref="J36:N37"/>
-    <mergeCell ref="F26:F28"/>
-    <mergeCell ref="H26:H28"/>
-    <mergeCell ref="A27:E28"/>
-    <mergeCell ref="J27:N28"/>
-    <mergeCell ref="F29:F31"/>
-    <mergeCell ref="H29:H31"/>
-    <mergeCell ref="A30:E31"/>
-    <mergeCell ref="J30:N31"/>
-    <mergeCell ref="F20:F22"/>
-    <mergeCell ref="H20:H22"/>
-    <mergeCell ref="A21:E22"/>
-    <mergeCell ref="J21:N22"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="H23:H25"/>
-    <mergeCell ref="A24:E25"/>
-    <mergeCell ref="J24:N25"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="J18:N19"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="A18:E19"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="F14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="A15:E16"/>
-    <mergeCell ref="J15:N16"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C11:D11"/>
@@ -7159,6 +7137,88 @@
     <mergeCell ref="D8:I8"/>
     <mergeCell ref="D10:I10"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="J18:N19"/>
+    <mergeCell ref="F17:F19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="A18:E19"/>
+    <mergeCell ref="D9:I9"/>
+    <mergeCell ref="F14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="A15:E16"/>
+    <mergeCell ref="J15:N16"/>
+    <mergeCell ref="F20:F22"/>
+    <mergeCell ref="H20:H22"/>
+    <mergeCell ref="A21:E22"/>
+    <mergeCell ref="J21:N22"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="H23:H25"/>
+    <mergeCell ref="A24:E25"/>
+    <mergeCell ref="J24:N25"/>
+    <mergeCell ref="F26:F28"/>
+    <mergeCell ref="H26:H28"/>
+    <mergeCell ref="A27:E28"/>
+    <mergeCell ref="J27:N28"/>
+    <mergeCell ref="F29:F31"/>
+    <mergeCell ref="H29:H31"/>
+    <mergeCell ref="A30:E31"/>
+    <mergeCell ref="J30:N31"/>
+    <mergeCell ref="F32:F34"/>
+    <mergeCell ref="H32:H34"/>
+    <mergeCell ref="A33:E34"/>
+    <mergeCell ref="J33:N34"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="H35:H37"/>
+    <mergeCell ref="A36:E37"/>
+    <mergeCell ref="J36:N37"/>
+    <mergeCell ref="F38:F40"/>
+    <mergeCell ref="H38:H40"/>
+    <mergeCell ref="A39:E40"/>
+    <mergeCell ref="J39:N40"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="A42:E43"/>
+    <mergeCell ref="J42:N43"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="A45:E46"/>
+    <mergeCell ref="J45:N46"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="H47:H49"/>
+    <mergeCell ref="A48:E49"/>
+    <mergeCell ref="J48:N49"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="A51:E52"/>
+    <mergeCell ref="J51:N52"/>
+    <mergeCell ref="F53:F55"/>
+    <mergeCell ref="H53:H55"/>
+    <mergeCell ref="A54:E55"/>
+    <mergeCell ref="J54:N55"/>
+    <mergeCell ref="F56:F58"/>
+    <mergeCell ref="H56:H58"/>
+    <mergeCell ref="A57:E58"/>
+    <mergeCell ref="J57:N58"/>
+    <mergeCell ref="F59:F61"/>
+    <mergeCell ref="H59:H61"/>
+    <mergeCell ref="A60:E61"/>
+    <mergeCell ref="J60:N61"/>
+    <mergeCell ref="F62:F64"/>
+    <mergeCell ref="H62:H64"/>
+    <mergeCell ref="A63:E64"/>
+    <mergeCell ref="J63:N64"/>
+    <mergeCell ref="F65:F67"/>
+    <mergeCell ref="H65:H67"/>
+    <mergeCell ref="A66:E67"/>
+    <mergeCell ref="J66:N67"/>
+    <mergeCell ref="F68:F70"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="A69:E70"/>
+    <mergeCell ref="J69:N70"/>
+    <mergeCell ref="F71:F73"/>
+    <mergeCell ref="H71:H73"/>
+    <mergeCell ref="A72:E73"/>
+    <mergeCell ref="J72:N73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7170,11 +7230,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="2" max="2" width="31.42578125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="31.44140625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="30">
@@ -7219,25 +7279,31 @@
         <v>74</v>
       </c>
       <c r="C12" s="23">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:4">
       <c r="B13" s="23" t="s">
         <v>75</v>
       </c>
+      <c r="C13" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="2:4">
       <c r="B14" s="23" t="s">
         <v>76</v>
       </c>
+      <c r="C14" s="23">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="2:4">
       <c r="B15" s="23" t="s">
         <v>77</v>
       </c>
       <c r="C15" s="23">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7257,6 +7323,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100AF28BDBD65D93F4BA99B6439AFEA320E" ma:contentTypeVersion="10" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="11d45d99e0339591c68aad091688ac92">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9b0ef35d-78e7-41bf-847f-3c0497ad5352" xmlns:ns3="3c969135-7855-44e0-a9fe-01d799f07605" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e603a3f7bf67670d682b80385fe4b00" ns2:_="" ns3:_="">
     <xsd:import namespace="9b0ef35d-78e7-41bf-847f-3c0497ad5352"/>
@@ -7457,12 +7529,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD7E773-5319-49CF-80DA-12E24FC51CD2}">
   <ds:schemaRefs>
@@ -7472,6 +7538,15 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5F7A0BD-DCD4-473A-A4BF-DC65A831158E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0FD9AFA-8FB8-4A5A-8D3C-E657A5B7F741}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7488,13 +7563,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5F7A0BD-DCD4-473A-A4BF-DC65A831158E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>